--- a/experiments/outputs/tables/table07_cv_results.xlsx
+++ b/experiments/outputs/tables/table07_cv_results.xlsx
@@ -472,7 +472,8 @@
     <col min="6" max="6" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="21.7109375" customWidth="1"/>
     <col min="8" max="8" width="22.7109375" customWidth="1"/>
-    <col min="9" max="10" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1097,19 +1098,19 @@
         <v>-0.1161858806320643</v>
       </c>
       <c r="F20">
-        <v>0.1599431740285159</v>
+        <v>0.159943174028516</v>
       </c>
       <c r="G20">
-        <v>0.3642870698077469</v>
+        <v>0.3642870698077468</v>
       </c>
       <c r="H20">
-        <v>0.04750732820812775</v>
+        <v>0.04750732820812776</v>
       </c>
       <c r="I20">
         <v>0.465425909762295</v>
       </c>
       <c r="J20">
-        <v>0.08335921587152618</v>
+        <v>0.08335921587152617</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1135,13 +1136,13 @@
         <v>0.3576424133131741</v>
       </c>
       <c r="H21">
-        <v>0.04772865838652511</v>
+        <v>0.0477286583865251</v>
       </c>
       <c r="I21">
         <v>0.4633969696068496</v>
       </c>
       <c r="J21">
-        <v>0.08150426474666736</v>
+        <v>0.08150426474666737</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1158,7 +1159,7 @@
         <v>28</v>
       </c>
       <c r="E22">
-        <v>-0.06458408819884026</v>
+        <v>-0.06458408819884033</v>
       </c>
       <c r="F22">
         <v>0.1925188483004346</v>
@@ -1170,10 +1171,10 @@
         <v>0.05186175953772144</v>
       </c>
       <c r="I22">
-        <v>0.4536246712061656</v>
+        <v>0.4536246712061657</v>
       </c>
       <c r="J22">
-        <v>0.08087653809270101</v>
+        <v>0.080876538092701</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1190,7 +1191,7 @@
         <v>26</v>
       </c>
       <c r="E23">
-        <v>-0.096903693447477</v>
+        <v>-0.09690369344747699</v>
       </c>
       <c r="F23">
         <v>0.08982468849945929</v>
@@ -1222,7 +1223,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>0.005167285994177572</v>
+        <v>0.00516728599417758</v>
       </c>
       <c r="F24">
         <v>0.1370053392092622</v>
@@ -1231,7 +1232,7 @@
         <v>0.3938237795796224</v>
       </c>
       <c r="H24">
-        <v>0.07504326653784675</v>
+        <v>0.07504326653784676</v>
       </c>
       <c r="I24">
         <v>0.5245235029630679</v>
@@ -1254,7 +1255,7 @@
         <v>28</v>
       </c>
       <c r="E25">
-        <v>-0.08505350971329613</v>
+        <v>-0.0850535097132961</v>
       </c>
       <c r="F25">
         <v>0.1299418025337843</v>
@@ -1295,7 +1296,7 @@
         <v>0.4036104502245728</v>
       </c>
       <c r="H26">
-        <v>0.07075658075294783</v>
+        <v>0.07075658075294781</v>
       </c>
       <c r="I26">
         <v>0.543344915616925</v>
@@ -1327,13 +1328,13 @@
         <v>0.3941363609103631</v>
       </c>
       <c r="H27">
-        <v>0.07007706556912546</v>
+        <v>0.07007706556912545</v>
       </c>
       <c r="I27">
         <v>0.5336719792711352</v>
       </c>
       <c r="J27">
-        <v>0.09993989806667299</v>
+        <v>0.09993989806667297</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1353,13 +1354,13 @@
         <v>-0.1516804915474919</v>
       </c>
       <c r="F28">
-        <v>0.1633932399173754</v>
+        <v>0.1633932399173753</v>
       </c>
       <c r="G28">
         <v>0.4044523859982908</v>
       </c>
       <c r="H28">
-        <v>0.06988886037635574</v>
+        <v>0.06988886037635572</v>
       </c>
       <c r="I28">
         <v>0.5427020467162491</v>
@@ -1722,7 +1723,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>-0.01979681973730355</v>
+        <v>-0.01979681973730354</v>
       </c>
       <c r="F40">
         <v>0.2569809512913426</v>
@@ -1748,10 +1749,10 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>-0.209486067234612</v>
+        <v>-0.2094860672346119</v>
       </c>
       <c r="F41">
-        <v>0.1801303265816856</v>
+        <v>0.1801303265816855</v>
       </c>
       <c r="G41">
         <v>0.4119279684675876</v>
@@ -1841,7 +1842,7 @@
         <v>-0.3259811606637577</v>
       </c>
       <c r="F44">
-        <v>0.5126829408423007</v>
+        <v>0.5126829408423005</v>
       </c>
       <c r="G44">
         <v>0.37697313438089</v>
@@ -1902,22 +1903,22 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>-0.01102348588286247</v>
+        <v>-0.01106468303907164</v>
       </c>
       <c r="F46">
-        <v>0.1522987591300826</v>
+        <v>0.1521033195394775</v>
       </c>
       <c r="G46">
-        <v>0.3542454235038573</v>
+        <v>0.3542695810347239</v>
       </c>
       <c r="H46">
-        <v>0.03594933730758775</v>
+        <v>0.03591840091356369</v>
       </c>
       <c r="I46">
-        <v>0.4332397073983076</v>
+        <v>0.4332476882733112</v>
       </c>
       <c r="J46">
-        <v>0.0447716771910716</v>
+        <v>0.04471973305673101</v>
       </c>
     </row>
     <row r="47" spans="1:10">
